--- a/data_extactor/batch_10_fa/batch_0084_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0084_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | نرم‌افزار نمایش نقشه | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP | نرم‌افزار ثبت زمان</t>
+          <t>Autodesk AutoCAD | Blueprint display software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP | نرم‌افزار ثبت زمان</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | درک مطلب خواندن</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | کامپیوتر و الکترونیک</t>
+          <t>تولید و فرآوری | مکانیک | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات دست و بازو | چالاکی انگشتان | چالاکی دست | حساسیت به مسئله | ترتیب‌دهی اطلاعات | دقت کنترل | تجسم فضایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ‌های بصری | بینایی دور | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک مطلب کتبی | درک مطلب شفاهی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | دقت کنترل | تجسم | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | بینایی دور | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | درک شفاهی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط‌های بسته، با کنترل دما | بحث‌های چهره‌به‌چهره با افراد و در قالب تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یک گروه کاری یا تیم یا مشارکت در آن | اهمیت دقیق یا درست بودن | ارتباط با دیگران | سلامت و ایمنی سایر کارگران | فشار زمانی | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | فشار زمانی | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، تجهیزات و سیستم‌های هواپیما | متخصصان و تکنسین‌های کالیبراسیون | اپراتورهای ابزار کنترل عددی کامپیوتری | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | نصاب‌ها و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | تکنسین‌ها و متخصصان مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصاب‌ها و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | ماشین‌کاران | آسیاب‌سازان | مدل‌سازان، فلز و پلاستیک | تکنسین‌های رباتیک | مونتاژکاران تیمی | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری و برنج‌کاری</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | اپراتورهای ابزار کنترل عددی کامپیوتری | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | ماشین‌کاران | مهندسان نصب ماشین‌آلات | مدل‌سازان فلز و پلاستیک | تکنسین‌های رباتیک | مونتاژکاران تیمی | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | Dassault Systemes SolidWorks | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP</t>
+          <t>نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Dassault Systemes SolidWorks | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب خواندن | پایش | تفکر انتقادی | سخن‌گفتن | گوش‌دادن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فرآوری | خدمات مشتریان و پرسنل</t>
+          <t>مکانیک | تولید و فرآوری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چالاکی دست | چالاکی انگشتان | بینایی نزدیک | تجسم فضایی | انعطاف‌پذیری بدنی | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک مطلب کتبی | درک مطلب شفاهی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | قدرت تنه</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | بینایی نزدیک | تجسم | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک کتبی | درک شفاهی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | قدرت تنه</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و در قالب تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان در حالت ایستاده | کار با یک گروه کاری یا تیم یا مشارکت در آن | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض تجهیزات خطرناک | دفعات تصمیم‌گیری | نزدیکی فیزیکی | صرف زمان برای خم کردن یا چرخاندن بدن | محیط‌های بسته، بدون کنترل دما | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای ایستادن | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | صرف زمان برای خم کردن یا چرخاندن بدن | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصاب‌ها و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌تراش و ابزار تراشکاری، فلز و پلاستیک | کارگران طرح‌بندی، فلز و پلاستیک | ماشین‌کاران | کارگران تعمیر و نگهداری، ماشین‌آلات | مهندسان مکانیک | آسیاب‌سازان | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مدل‌سازان، فلز و پلاست | تعمیرکاران واگن‌های ریلی | سازندگان و مونتاژکاران فلزات سازه‌ای | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری و برنج‌کاری</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | کارگران شابلون‌زنی، فلز و پلاستیک | ماشین‌کاران | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان مکانیک | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مدل‌سازان فلز و پلاستیک | تعمیرکنندگان واگن‌های ریلی | سازندگان و مونتاژکاران فلزات سازه‌ای | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | Dassault Systemes CATIA | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار Tekla | نرم‌افزار مدل‌سازی سه‌بعدی</t>
+          <t>نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Dassault Systemes CATIA | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار Tekla | نرم‌افزار مدل‌سازی سه‌بعدی</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | درک مطلب خواندن | تفکر انتقادی | سخن‌گفتن</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | بینایی نزدیک | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | چالاکی دست | تجسم فضایی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | قدرت تنه | چالاکی انگشتان</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | مهارت دستی | تجسم | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | قدرت تنه | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | بحث‌های چهره‌به‌چهره با افراد و در قالب تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | محیط‌های بسته، بدون کنترل دما | اهمیت دقیق یا درست بودن | فشار زمانی | صرف زمان در حالت ایستاده | ارتباط با دیگران | کار با یک گروه کاری یا تیم یا مشارکت در آن | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارگران | صرف زمان برای انجام حرکات تکراری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | محیط داخلی، بدون کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | فشار زمانی | صرف زمان برای ایستادن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | نجاران | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران سنگ‌زنی و پرداخت دستی | کارگران طرح‌بندی، فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و رنده، فلز و پلاستیک | آسیاب‌سازان | مدل‌سازان، فلز و پلاست | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | الگو‌سازان، فلز و پلاستیک | کارگران میلگرد و آهن تقویتی | کارگران ورق‌کار | کارگران آهن و فولاد سازه‌ای | ابزارسازان و قالب‌سازان | جوشکاران، برش‌کاران، لحیم‌کاران و برنج‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری و برنج‌کاری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | نجّاران | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران سنگ‌زنی و پرداخت دستی | کارگران شابلون‌زنی، فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مهندسان نصب ماشین‌آلات | مدل‌سازان فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | الگوسازان فلز و پلاستیک | کارگران آهن تقویتی و میلگرد | کارگران ورق‌کاری | کارگران سازه‌های آهنی و فولادی | سازندگان ابزار و قالب | جوشکاران، برش‌کاران، لحیم‌کاران نرم و لحیم‌کاران سخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>پایش | سخن‌گفتن | گوش‌دادن فعال | درک مطلب خواندن</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>اداره و مدیریت | تولید و فرآوری | آموزش و پرورش | شیمی | زبان انگلیسی | خدمات مشتریان و پرسنل</t>
+          <t>مدیریت و اداره | تولید و فرآوری | آموزش و پرورش | شیمی | زبان انگلیسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | ثبات دست و بازو | هماهنگی چند عضو | قدرت تنه | بینایی نزدیک | درک مطلب شفاهی | ترتیب‌دهی اطلاعات | تجسم فضایی | انعطاف‌پذیری بدنی | تشخیص رنگ‌های بصری | قدرت ایستا | دقت کنترل | چالاکی دست | توجه انتخابی | انعطاف‌پذیری بستار | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک مطلب کتبی | چالاکی انگشتان | وضوح گفتار | تشخیص گفتار | استقامت بدنی</t>
+          <t>حساسیت به مسئله | ثبات دست و بازو | هماهنگی چند عضو | قدرت تنه | بینایی نزدیک | درک شفاهی | ترتیب‌دهی اطلاعات | تجسم | انعطاف‌پذیری دامنه حرکت | تشخیص رنگ بصری | قدرت ایستا | دقت کنترل | مهارت دستی | توجه انتخابی | انعطاف‌پذیری بستار | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | مهارت انگشتان | وضوح گفتار | تشخیص گفتار | استقامت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>صرف زمان در حالت ایستاده | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | بحث‌های چهره‌به‌چهره با افراد و در قالب تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نزدیکی فیزیکی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یک گروه کاری یا تیم یا مشارکت در آن | صرف زمان برای انجام حرکات تکراری | ارتباط با دیگران | صرف زمان برای خم کردن یا چرخاندن بدن | پیامدهای کاری و نتایج سایر کارگران | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض شرایط خطرناک | اهمیت دقیق یا درست بودن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | اهمیت تکرار وظایف یکسان</t>
+          <t>صرف زمان برای ایستادن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نزدیکی فیزیکی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | ارتباط با دیگران | صرف زمان برای خم کردن یا چرخاندن بدن | پیامدهای کاری و نتایج سایر کارکنان | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض شرایط خطرناک | اهمیت دقیق یا درست بودن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | مونتاژکاران سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌آمیزی و پاشش | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران سیم‌پیچ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و شکل‌دهی، الیاف مصنوعی و شیشه‌ای | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | کارگران عایق‌کاری، کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری، فلز و پلاستیک | کارگران رنگ‌آمیزی، پوشش‌دهی و تزئین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آبکاری، فلز و پلاستیک | تعمیرکاران مواد نسوز، به جز بناها | سازندگان و مونتاژکاران فلزات سازه‌ای | تایر سازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | کارگران نقاشی، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | تعمیرکاران مواد نسوز، به جز بناهای آجرکار | سازندگان و مونتاژکاران فلزات سازه‌ای | تایر سازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>پایش | تفکر انتقادی | گوش‌دادن فعال | درک مطلب خواندن | سخن‌گفتن | ریاضیات</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>چالاکی انگشتان | ثبات دست و بازو | بینایی نزدیک | چالاکی دست | حساسیت به مسئله | دقت کنترل | تجسم فضایی | ترتیب‌دهی اطلاعات | درک مطلب شفاهی | تشخیص رنگ‌های بصری | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان شفاهی</t>
+          <t>مهارت انگشتان | ثبات دست و بازو | بینایی نزدیک | مهارت دستی | حساسیت به مسئله | دقت کنترل | تجسم | ترتیب‌دهی اطلاعات | درک شفاهی | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در قالب تیم‌ها | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | محیط‌های بسته، با کنترل دما | دفعات تصمیم‌گیری | مکالمات تلفنی | کار با یک گروه کاری یا تیم یا مشارکت در آن | اهمیت دقیق یا درست بودن | صرف زمان در حالت نشسته</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، تجهیزات و سیستم‌های هواپیما | متخصصان و تکنسین‌های کالیبراسیون | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران سیم‌پیچ | نصاب‌ها و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌تراش و ابزار تراشکاری، فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و رنده، فلز و پلاستیک | مدل‌سازان، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندگانه، فلز و پلاستیک | سازندگان و مونتاژکاران فلزات سازه‌ای | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار | ابزارسازان و قالب‌سازان | تعمیرکاران ساعت‌های مچی و دیواری</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | سازندگان و مونتاژکاران فلزات سازه‌ای | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تعمیرکاران ساعت مچی و دیواری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | پایش | تفکر انتقادی | سخن‌گفتن | درک مطلب خواندن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | امنیت و ایمنی عمومی | زبان انگلیسی | آموزش و پرورش | کامپیوتر و الکترونیک | طراحی | مهندسی و فناوری | ریاضیات | اداره و مدیریت</t>
+          <t>تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | طراحی | مهندسی و فناوری | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>چالاکی دست | چالاکی انگشتان | بینایی نزدیک | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | ثبات دست و بازو | استدلال قیاسی | حساسیت به مسئله | درک مطلب شفاهی | قدرت تنه | دقت کنترل | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | بیان شفاهی | درک مطلب کتبی | بینایی دور</t>
+          <t>مهارت دستی | مهارت انگشتان | بینایی نزدیک | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | ثبات دست و بازو | استدلال قیاسی | حساسیت به مسئله | درک شفاهی | قدرت تنه | دقت کنترل | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | بیان شفاهی | درک کتبی | بینایی دور</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و در قالب تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | کار با یک گروه کاری یا تیم یا مشارکت در آن | ارتباط با دیگران | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | محیط‌های بسته، با کنترل دما | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | دفعات تصمیم‌گیری | صرف زمان در حالت ایستاده | تعیین وظایف، اولویت‌ها و اهداف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | صرف زمان برای ایستادن | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و متخصصان مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | سرپرستان خط اول کارگران تولید و عملیاتی | تکنسین‌ها و متخصصان مهندسی صنایع | مهندسان صنایع | مکانیک‌های ماشین‌آلات صنعتی | مدیران تولید صنعتی | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌گیرها و توزین‌کنندگان | ماشین‌کاران | مهندسان تولید | تکنسین‌ها و متخصصان مهندسی مکانیک | مهندسان مکانیک | آسیاب‌سازان | تکنسین‌های رباتیک | سازندگان و مونتاژکاران فلزات سازه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری و برنج‌کاری</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | سرپرستان رده اول کارگران تولید و بهره‌برداری | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مکانیک‌های ماشین‌آلات صنعتی | مدیران تولید صنعتی | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | ماشین‌کاران | مهندسان تولید | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان نصب ماشین‌آلات | تکنسین‌های رباتیک | سازندگان و مونتاژکاران فلزات سازه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | سیستم مدیریت نگهداری و تعمیرات کامپیوتری CMMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار پایگاه داده | نرم‌افزار SAP</t>
+          <t>نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | سیستم مدیریت نگهداری کامپیوتری CMMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار پایگاه داده | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>پایش | گوش‌دادن فعال | تفکر انتقادی | درک مطلب خواندن | سخن‌گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | طراحی | کامپیوتر و الکترونیک</t>
+          <t>تولید و فرآوری | مکانیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | طراحی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چالاکی دست | چالاکی انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت بدنی | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری بدنی | زمان عکس‌العمل | حساسیت به مسئله | درک مطلب شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>محیط‌های بسته، بدون کنترل دما | صرف زمان در حالت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارگران | پیامد خطا | درجه اتوماسیون | اهمیت تکرار وظایف یکسان | بحث‌های چهره‌به‌چهره با افراد و در قالب تیم‌ها | کار با یک گروه کاری یا تیم یا مشارکت در آن | اهمیت دقیق یا درست بودن</t>
+          <t>محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارکنان | پیامد خطا | میزان خودکارسازی | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مونتاژکاران تیمی | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | سازندگان و مونتاژکاران فلزات سازه‌ای | لمینت‌کاران و سازندگان فایبرگلاس | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران سیم‌پیچ | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | مونتاژکاران سازه، سطوح، تجهیزات و سیستم‌های هواپیما | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌گیرها و توزین‌کنندگان | ماشین‌کاران | جوشکاران، برش‌کاران، لحیم‌کاران و برنج‌کاران | دستیاران--کارگران تولید | کارگران تولید، سایر موارد | سرپرستان خط اول کارگران تولید و عملیاتی | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | اپراتورهای ابزار کنترل عددی کامپیوتری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندگانه، فلز و پلاستیک | تکنسین‌های فرآوری نیمه‌هادی‌ها</t>
+          <t>مونتاژکاران تیمی | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | سازندگان و مونتاژکاران فلزات سازه‌ای | لمینت‌کاران و سازندگان فایبرگلاس | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | ماشین‌کاران | جوشکاران، برش‌کاران، لحیم‌کاران نرم و لحیم‌کاران سخت | کمک‌کاران--کارگران تولید | کارگران تولید، سایر موارد | سرپرستان رده اول کارگران تولید و بهره‌برداری | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | اپراتورهای ابزار کنترل عددی کامپیوتری | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تکنسین‌های فرآوری نیمه‌رساناها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>پایش | سخن‌گفتن | گوش‌دادن فعال | یادگیری فعال | تفکر انتقادی</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | یادگیری فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | خدمات مشتریان و پرسنل | تولید مواد غذایی | زبان انگلیسی | ریاضیات</t>
+          <t>تولید و فرآوری | خدمات مشتری و شخصی | تولید مواد غذایی | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | درک مطلب شفاهی | تشخیص گفتار | تشخیص رنگ‌های بصری | حساسیت به مسئله | بیان شفاهی | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک مطلب کتبی | وضوح گفتار | دقت کنترل | چالاکی انگشتان | چالاکی دست | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بینایی نزدیک | درک شفاهی | تشخیص گفتار | تشخیص رنگ بصری | حساسیت به مسئله | بیان شفاهی | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک کتبی | وضوح گفتار | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | صرف زمان در حالت ایستاده | فشار زمانی | بحث‌های چهره‌به‌چهره با افراد و در قالب تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | کار با یک گروه کاری یا تیم یا مشارکت در آن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | مکالمات تلفنی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارگران | محیط‌های بسته، با کنترل دما | صرف زمان برای انجام حرکات تکراری | دفعات تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ارتباط با دیگران | صرف زمان برای ایستادن | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>قصابان و برش‌دهندگان گوش | سرآشپزها و سرپرستان آشپزان | آشپزها، غذای آماده | آشپزها، موسسات و سلف‌سرویس‌ها | آشپزها، رستوران | آشپزها، سفارش‌های سریع | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، سنگ‌زنی و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، شکل‌دهی، پرس و متراکم‌سازی | کارکنان فست‌فود و پیشخوان | فرموله‌کنندگان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | اپراتورهای ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندی‌کنندگان و سورترها، محصولات کشاورزی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندها و عدل‌بندهای دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتر کردن، شفاف‌سازی، رسوب‌دهی و تقطیر</t>
+          <t>قصابان و برش‌دهندگان گوش | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزها، رستوران | آشپزها، سفارش‌های فوری | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران فست فود و پیشخوان | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | پایش | تفکر انتقادی | سخن‌گفتن | درک مطلب خواندن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنل | تولید مواد غذایی | تولید و فرآوری | بازاریابی و فروش</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | تولید و فرآوری | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | چالاکی دست | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بیان شفاهی | درک مطلب شفاهی | توجه انتخابی | قدرت تنه | چالاکی انگشتان | وضوح گفتار | تشخیص گفتار | تشخیص رنگ‌های بصری</t>
+          <t>بینایی نزدیک | مهارت دستی | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بیان شفاهی | درک شفاهی | توجه انتخابی | قدرت تنه | مهارت انگشتان | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>محیط‌های بسته، با کنترل دما | صرف زمان در حالت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | برخورد با مشتریان خارجی یا عموم مردم | کار با یک گروه کاری یا تیم یا مشارکت در آن | بحث‌های چهره‌به‌چهره با افراد و در قالب تیم‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | نزدیکی فیزیکی | دفعات تصمیم‌گیری | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارگران | پیامد خطا | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | پیامدهای کاری و نتایج سایر کارگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سرعت تعیین‌شده توسط سرعت تجهیزات | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای خم کردن یا چرخاندن بدن</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | پیامد خطا | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سرعت تعیین‌شده توسط سرعت تجهیزات | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای خم کردن یا چرخاندن بدن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>نانوایان | سرآشپزها و سرپرستان آشپزان | آشپزها، فست‌فود | آشپزها، موسسات و سلف‌سرویس‌ها | آشپزها، خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های سریع | کارکنان فست‌فود و پیشخوان | سرپرستان خط اول کارگران آماده‌سازی و سرو مواد غذایی | فرموله‌کنندگان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | دانشمندان و متخصصان صنایع غذایی | سروکنندگان مواد غذایی، غیررستورانی | مدیران خدمات غذایی | اپراتورهای ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندی‌کنندگان و سورترها، محصولات کشاورزی | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | بسته‌بندها و عدل‌بندهای دستی | ذبح‌کنندگان و بسته‌بندهای گوشت</t>
+          <t>نانوایان | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | کارگران فست فود و پیشخوان | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | دانشمندان و تکنولوژیست‌های علوم غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | بسته‌بندهای دستی | ذبح‌کنندگان و بسته‌بندندگان گوشت</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | پایش | تفکر انتقادی | سخن‌گفتن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | تولید مواد غذایی | امنیت و ایمنی عمومی | ریاضیات | اداره و مدیریت | مکانیک | پرسنل و منابع انسانی | ترابری | آموزش و پرورش</t>
+          <t>تولید و فرآوری | تولید مواد غذایی | ایمنی و امنیت عمومی | ریاضیات | مدیریت و اداره | مکانیک | پرسنل و منابع انسانی | حمل و نقل | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | قدرت تنه | چالاکی دست | توجه انتخابی | بیان شفاهی | هماهنگی چند عضو | چالاکی انگشتان | تجسم فضایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک مطلب شفاهی | وضوح گفتار | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | قدرت تنه | مهارت دستی | توجه انتخابی | بیان شفاهی | هماهنگی چند عضو | مهارت انگشتان | تجسم | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک شفاهی | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>صرف زمان در حالت ایستاده | صرف زمان برای انجام حرکات تکراری | محیط‌های بسته، با کنترل دما | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | دفعات تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | کار با یک گروه کاری یا تیم یا مشارکت در آن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | سرعت تعیین‌شده توسط سرعت تجهیزات | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | صرف زمان برای خم کردن یا چرخاندن بدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | بحث‌های چهره‌به‌چهره با افراد و در قالب تیم‌ها | پیامدهای کاری و نتایج سایر کارگران | پیامد خطا | اهمیت تکرار وظایف یکسان</t>
+          <t>صرف زمان برای ایستادن | صرف زمان برای انجام حرکات تکراری | محیط داخلی، دارای کنترل شرایط محیطی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | سرعت تعیین‌شده توسط سرعت تجهیزات | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای خم کردن یا چرخاندن بدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پیامدهای کاری و نتایج سایر کارکنان | پیامد خطا | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نانوایان | قصابان و برش‌دهندگان گوش | آشپزها، رستوران | آشپزها، سفارش‌های سریع | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، سنگ‌زنی و پرداخت | برش‌دهندگان و پاک‌کنندگان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کن | کارگران مزارع و کارگران ساده، محصولات زراعی، گلخانه‌ای و نهالستان | کارگران مزارع، حیوانات مزرعه، دامداری و آبزی‌پروری | فرموله‌کنندگان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | اپراتورهای ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندی‌کنندگان و سورترها، محصولات کشاورزی | کارگران ساده و جابجا‌کنندگان دستی بار، کالا و مواد | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندها و عدل‌بندهای دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتر کردن، شفاف‌سازی، رسوب‌دهی و تقطیر | ذبح‌کنندگان و بسته‌بندهای گوش</t>
+          <t>نانوایان | قصابان و برش‌دهندگان گوش | آشپزها، رستوران | آشپزها، سفارش‌های فوری | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | کارگران کشاورزی، حیوانات مزرعه، دامداری و آبزی‌پروری | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | ذبح‌کنندگان و بسته‌بندندگان گوشت</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0084_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0084_fa.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | نرم‌افزار نمایش نقشه‌های فنی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP | نرم‌افزار ثبت ساعت کار و حضور و غیاب</t>
+          <t>Autodesk AutoCAD | Blueprint display software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP | نرم‌افزار ثبت زمان</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | پایداری دست و بازو | چابکی انگشتان | چابکی دستی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دقت کنترل | تجسم فضایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ‌ها | دید دور | انعطاف‌پذیری بستن | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | درک شفاهی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | دقت کنترل | تجسم | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | بینایی دور | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | درک شفاهی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | کارشناسان و تکنسین‌های کالیبراسیون | اپراتورهای ماشین‌های ابزار CNC | برنامه‌نویسان ماشین‌های ابزار CNC | نصابان و تعمیرکاران کنترل‌ها و شیرآلات، به‌جز درهای مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات مرتبط | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی در وسایل نقلیه | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مهندسان الکترونیک، به‌جز رایانه | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | ماشین‌کاران | متخصصان نصب و راه‌اندازی ماشین‌آلات صنعتی (Millwrights) | مدل‌سازان فلزی و پلاستیکی | تکنسین‌های رباتیک | مونتاژکاران گروهی | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری و لحیم‌کاری</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌ها و کارشناسان فنی کالیبراسیون | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مهندسان الکترونیک، به‌جز کامپیوتر | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مدل‌سازان فلز و پلاستیک | تکنسین‌های رباتیک | مونتاژکاران گروهی | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار طراحی و نقشه‌کشی رایانه‌ای CADD | Dassault Systemes SolidWorks | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP</t>
+          <t>نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Dassault Systemes SolidWorks | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فرآوری | خدمات مشتریان و خدمات فردی</t>
+          <t>مکانیک | تولید و فرآوری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | چابکی دستی | چابکی انگشتان | دید نزدیک | تجسم فضایی | انعطاف‌پذیری دامنه حرکتی | قدرت ایستا | هماهنگی چند عضو بدن | دقت کنترل | مرتب‌سازی اطلاعات | حساسیت به مسئله | درک کتبی | درک شفاهی | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری بستن | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | قدرت بالاتنه</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | بینایی نزدیک | تجسم | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک کتبی | درک شفاهی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | قدرت تنه</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | دیگ‌سازان (بویلرسازان) | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصابان و تعمیرکاران کنترل‌ها و شیرآلات، به‌جز درهای مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات مرتبط | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تراشکاری فلز و پلاستیک | خط‌کش‌ها و قالب‌ریزان فلزی و پلاستیکی | ماشین‌کاران | کارگران تعمیرات و نگهداری ماشین‌آلات | مهندسان مکانیک | متخصصان نصب و راه‌اندازی ماشین‌آلات صنعتی (Millwrights) | مکانیک‌های ماشین‌آلات سنگین متحرک، به‌جز موتور | مدل‌سازان فلزی و پلاستیکی | تعمیرکاران واگن‌های ریلی | سازندگان و مونتاژکاران سازه‌های فلزی | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری و لحیم‌کاری</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان مکانیک | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | مدل‌سازان فلز و پلاستیک | تعمیرکار واگن قطار | سازندگان و مونتاژکاران سازه‌های فلزی | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار طراحی و نقشه‌کشی رایانه‌ای CADD | Dassault Systemes CATIA | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار Tekla | نرم‌افزار مدل‌سازی سه‌بعدی</t>
+          <t>نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Dassault Systemes CATIA | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار Tekla | نرم‌افزار مدل‌سازی سه‌بعدی</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | دید نزدیک | قدرت ایستا | هماهنگی چند عضو بدن | دقت کنترل | چابکی دستی | تجسم فضایی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | قدرت بالاتنه | چابکی انگشتان</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | مهارت دستی | تجسم | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | قدرت تنه | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | دیگ‌سازان (بویلرسازان) | نجاران | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | پرداخت‌کاران و صیقل‌کاران دستی | خط‌کش‌ها و قالب‌ریزان فلزی و پلاستیکی | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه تراش فلز و پلاستیک | متخصصان نصب و راه‌اندازی ماشین‌آلات صنعتی (Millwrights) | مدل‌سازان فلزی و پلاستیکی | قالب‌ریزان و شکل‌دهندگان، به‌جز فلز و پلاستیک | الگو‌سازان فلز و پلاستیک | آرماتوربندان | کارگران ورق‌کاری | اسکلت‌سازان سازه‌های فلزی و فولادی | قالب‌سازان و ابزارسازان صنعتی | جوشکاران، برشکاران و لحیم‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان و اپراتورهای ماشین‌های چوب‌بری، به‌جز اره‌کشی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | نجاران و درودگران | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مدل‌سازان فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | الگوسازان فلز و پلاستیک | آرماتوربندان و نصابان میلگرد | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی | قالب‌سازان و ابزارسازان صنعتی | جوشکاران، برشکاران و لحیم‌کاران صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | تولید و فرآوری | آموزش و پرورش | شیمی | زبان انگلیسی | خدمات مشتریان و خدمات فردی</t>
+          <t>مدیریت و اداره | تولید و فرآوری | آموزش و پرورش | شیمی | زبان انگلیسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | پایداری دست و بازو | هماهنگی چند عضو بدن | قدرت بالاتنه | دید نزدیک | درک شفاهی | مرتب‌سازی اطلاعات | تجسم فضایی | انعطاف‌پذیری دامنه حرکتی | تشخیص رنگ‌ها | قدرت ایستا | دقت کنترل | چابکی دستی | توجه انتخابی | انعطاف‌پذیری بستن | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | چابکی انگشتان | وضوح گفتار | تشخیص گفتار | استقامت بدنی</t>
+          <t>حساسیت به مسئله | ثبات دست و بازو | هماهنگی چند عضو | قدرت تنه | بینایی نزدیک | درک شفاهی | ترتیب‌دهی اطلاعات | تجسم | انعطاف‌پذیری دامنه حرکت | تشخیص رنگ بصری | قدرت ایستا | دقت کنترل | مهارت دستی | توجه انتخابی | انعطاف‌پذیری بستار | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | مهارت انگشتان | وضوح گفتار | تشخیص گفتار | استقامت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌آلات چسب‌زنی و اتصال | مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | پیچندگان بوبین، نوارپیچ‌ها و پرداخت‌کاران سیم‌پیچ | تنظیم‌کنندگان و متصدیان دستگاه‌های برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکستروژن و فرم‌دهی الیاف مصنوعی و شیشه‌ای | قالب‌ریزان و ماهیچه‌سازان ریخته‌گری | رنگ‌کاران و رویه‌کوبان مبلمان | پرداخت‌کاران و صیقل‌کاران دستی | عایق‌کاران کف، سقف و دیوار ساختمانی | عایق‌کاران تجهیزات مکانیکی و لوله‌کشی | اپراتورهای تغذیه و تخلیه ماشین‌آلات تولید | قالب‌ریزان و شکل‌دهندگان، به‌جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | کارگران رنگ‌آمیزی صنعتی، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آبکاری فلز و پلاستیک | تعمیرکاران سازه‌های نسوز، به‌جز بنّاها | سازندگان و مونتاژکاران سازه‌های فلزی | تایرسازان صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌های چوب‌بری، به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی | سازندگان و مونتاژکاران سازه‌های فلزی | سازندگان تایر | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | ریاضیات</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | پایداری دست و بازو | دید نزدیک | چابکی دستی | حساسیت به مسئله | دقت کنترل | تجسم فضایی | مرتب‌سازی اطلاعات | درک شفاهی | تشخیص رنگ‌ها | انعطاف‌پذیری طبقه‌بندی | استدلال قیاسی | بیان شفاهی</t>
+          <t>مهارت انگشتان | ثبات دست و بازو | بینایی نزدیک | مهارت دستی | حساسیت به مسئله | دقت کنترل | تجسم | ترتیب‌دهی اطلاعات | درک شفاهی | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | کارشناسان و تکنسین‌های کالیبراسیون | پیچندگان بوبین، نوارپیچ‌ها و پرداخت‌کاران سیم‌پیچ | نصابان و تعمیرکاران کنترل‌ها و شیرآلات، به‌جز درهای مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات مرتبط | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | پرداخت‌کاران و صیقل‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پرداخت، لپینگ و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تراشکاری فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه تراش فلز و پلاستیک | مدل‌سازان فلزی و پلاستیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های ابزار چندمنظوره فلز و پلاستیک | سازندگان و مونتاژکاران سازه‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان صنعتی | تعمیرکاران ساعت دیواری و مچی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌ها و کارشناسان فنی کالیبراسیون | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | سازندگان و مونتاژکاران سازه‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تعمیرکاران ساعت‌های مچی و دیواری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | طراحی | مهندسی و فناوری | ریاضیات | مدیریت و امور اداری</t>
+          <t>تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | طراحی | مهندسی و فناوری | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | دید نزدیک | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | پایداری دست و بازو | استدلال قیاسی | حساسیت به مسئله | درک شفاهی | قدرت بالاتنه | دقت کنترل | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | بیان کتبی | بیان شفاهی | درک کتبی | دید دور</t>
+          <t>مهارت دستی | مهارت انگشتان | بینایی نزدیک | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | ثبات دست و بازو | استدلال قیاسی | حساسیت به مسئله | درک شفاهی | قدرت تنه | دقت کنترل | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | بیان شفاهی | درک کتبی | بینایی دور</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | سرپرستان رده اول کارگران تولید و عملیات | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مکانیک‌های ماشین‌آلات صنعتی | مدیران تولید صنعتی | بازرسان، آزمایش‌گران، تفکیک‌کنندگان، نمونه‌برداران و وزن‌کنندگان در خط تولید | ماشین‌کاران | مهندسان ساخت و تولید | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | متخصصان نصب و راه‌اندازی ماشین‌آلات صنعتی (Millwrights) | تکنسین‌های رباتیک | سازندگان و مونتاژکاران سازه‌های فلزی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری و لحیم‌کاری</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | سرپرستان رده اول کارگران تولید و عملیات | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مکانیک‌های ماشین‌آلات صنعتی | مدیران تولید صنعتی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | مهندسان تولید و ساخت | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | تکنسین‌های رباتیک | سازندگان و مونتاژکاران سازه‌های فلزی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | پایداری دست و بازو | هماهنگی چند عضو بدن | دقت کنترل | قدرت ایستا | قدرت بالاتنه | استقامت بدنی | دید نزدیک | دید دور | ادراک عمق | هماهنگی حرکتی کل بدن | تعادل کل بدن | انعطاف‌پذیری دامنه حرکتی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مونتاژکاران گروهی | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | سازندگان و مونتاژکاران سازه‌های فلزی | لایه‌نشانان و سازندگان فایبرگلاس | پیچندگان بوبین، نوارپیچ‌ها و پرداخت‌کاران سیم‌پیچ | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | بازرسان، آزمایش‌گران، تفکیک‌کنندگان، نمونه‌برداران و وزن‌کنندگان در خط تولید | ماشین‌کاران | جوشکاران، برشکاران و لحیم‌کاران | کارگران ساده تولید | سایر کارگران حوزه تولید | سرپرستان رده اول کارگران تولید و عملیات | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | اپراتورهای ماشین‌های ابزار CNC | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های ابزار چندمنظوره فلز و پلاستیک | تکنسین‌های فرآوری نیمه‌هادی‌ها</t>
+          <t>مونتاژکاران گروهی | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | سازندگان و مونتاژکاران سازه‌های فلزی | لایه‌نشانان و سازندگان فایبرگلاس | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | جوشکاران، برشکاران و لحیم‌کاران صنعتی | کمک‌کارگران خطوط تولید | سایر کارگران خطوط تولید | سرپرستان رده اول کارگران تولید و عملیات | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تکنسین‌های فرآوری و ساخت نیمه‌هادی‌ها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | یادگیری فعال | تفکر انتقادی</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | یادگیری فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | خدمات مشتریان و خدمات فردی | تولید مواد غذایی | زبان انگلیسی | ریاضیات</t>
+          <t>تولید و فرآوری | خدمات مشتری و شخصی | تولید مواد غذایی | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | تشخیص گفتار | تشخیص رنگ‌ها | حساسیت به مسئله | بیان شفاهی | مرتب‌سازی اطلاعات | استدلال قیاسی | درک کتبی | وضوح گفتار | دقت کنترل | چابکی انگشتان | چابکی دستی | پایداری دست و بازو | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>بینایی نزدیک | درک شفاهی | تشخیص گفتار | تشخیص رنگ بصری | حساسیت به مسئله | بیان شفاهی | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک کتبی | وضوح گفتار | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>قصابان و خردکنندگان گوشت | سرآشپزان و سرآشپزان ارشد | آشپزان فست‌فود | آشپزان سازمان‌ها، مراکز اداری و سلف‌سرویس‌ها | آشپزان رستوران | آشپزان سفارش‌های فوری | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های خردایش و آسیاب مواد غذایی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و اسلایس مواد غذایی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، فرم‌دهی و پرس مواد غذایی | کارگران پیشخوان و فست‌فود | مسئولان آماده‌سازی و ترکیب فرمولاسیون مواد غذایی (Food Batchmakers) | اپراتورها و متصدیان دستگاه‌های پخت مواد غذایی | کارگران آماده‌سازی غذا | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کن صنعتی | درجه‌بندی‌کنندگان و تفکیک‌کنندگان محصولات کشاورزی | اپراتورهای تغذیه و تخلیه ماشین‌آلات تولید | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اختلاط و میکس مواد غذایی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جداسازی، فیلتراسیون و تقطیر مواد غذایی</t>
+          <t>قصابان و برش‌کاران گوشت | سرآشپزان و آشپزان ارشد | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان رستوران | آشپزان غذاهای فوری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | کارگران پیشخوان و فست‌فود | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | کارگران آماده‌سازی غذا | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید مواد غذایی | تولید و فرآوری | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | تولید و فرآوری | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی دستی | پایداری دست و بازو | دقت کنترل | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | حساسیت به مسئله | بیان شفاهی | درک شفاهی | توجه انتخابی | قدرت بالاتنه | چابکی انگشتان | وضوح گفتار | تشخیص گفتار | تشخیص رنگ‌ها</t>
+          <t>بینایی نزدیک | مهارت دستی | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بیان شفاهی | درک شفاهی | توجه انتخابی | قدرت تنه | مهارت انگشتان | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>نانوایان و شیرینی‌پزان | سرآشپزان و سرآشپزان ارشد | آشپزان فست‌فود | آشپزان سازمان‌ها، مراکز اداری و سلف‌سرویس‌ها | آشپزان منازل خصوصی | آشپزان رستوران | آشپزان سفارش‌های فوری | کارگران پیشخوان و فست‌فود | سرپرستان رده اول کارگران آماده‌سازی و سرو غذا | مسئولان آماده‌سازی و ترکیب فرمولاسیون مواد غذایی (Food Batchmakers) | اپراتورها و متصدیان دستگاه‌های پخت مواد غذایی | کارگران آماده‌سازی غذا | متخصصان و کارشناسان علوم و صنایع غذایی | مهمانداران و نیروهای پذیرایی و توزیع غذا، خارج از رستوران | مدیران خدمات پذیرایی و غذا | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کن صنعتی | درجه‌بندی‌کنندگان و تفکیک‌کنندگان محصولات کشاورزی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | بسته‌بندهای دستی | سلاخان و کارگران کشتارگاه و بسته‌بندی گوشت</t>
+          <t>نانوایان و شیرینی‌پزان | سرآشپزان و آشپزان ارشد | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی و سرآشپزان شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | کارگران آماده‌سازی غذا | متخصصان و کارشناسان علوم و صنایع غذایی | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | کارگران بسته‌بندی دستی | قصابان و بسته‌بندی‌کنندگان گوشت</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | تولید مواد غذایی | ایمنی و امنیت عمومی | ریاضیات | مدیریت و امور اداری | مکانیک | امور اداری و منابع انسانی | ترابری و حمل‌ونقل | آموزش و پرورش</t>
+          <t>تولید و فرآوری | تولید مواد غذایی | ایمنی و امنیت عمومی | ریاضیات | مدیریت و اداره | مکانیک | پرسنل و منابع انسانی | حمل و نقل | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | دقت کنترل | دید نزدیک | قدرت بالاتنه | چابکی دستی | توجه انتخابی | بیان شفاهی | هماهنگی چند عضو بدن | چابکی انگشتان | تجسم فضایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | درک شفاهی | وضوح گفتار | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | قدرت تنه | مهارت دستی | توجه انتخابی | بیان شفاهی | هماهنگی چند عضو | مهارت انگشتان | تجسم | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک شفاهی | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نانوایان و شیرینی‌پزان | قصابان و برش‌کاران گوشت | آشپزان رستوران | آشپزان سفارش‌های فوری | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های خردایش و آسیاب مواد غذایی | برش‌کاران دستی مواد و کالاها | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و اسلایس مواد غذایی | کارگران مزارع، نهالستان‌ها و گلخانه‌ها | کارگران مزارع پرورش دام، طیور و آبزی‌پروری | مسئولان آماده‌سازی و ترکیب فرمولاسیون مواد غذایی (Food Batchmakers) | اپراتورها و متصدیان دستگاه‌های پخت مواد غذایی | کارگران آماده‌سازی غذا | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کن صنعتی | درجه‌بندی‌کنندگان و تفکیک‌کنندگان محصولات کشاورزی | کارگران باربری و جابجایی دستی کالا و مواد | اپراتورهای تغذیه و تخلیه ماشین‌آلات تولید | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جداسازی، فیلتراسیون و تقطیر مواد غذایی | سلاخان و کارگران کشتارگاه و بسته‌بندی گوشت</t>
+          <t>نانوایان و شیرینی‌پزان | قصابان و برش‌کاران گوشت | آشپزان رستوران | آشپزان غذاهای فوری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | کارگران زراعت، نهالستان و گلخانه | کارگران پرورش دام، طیور و آبزیان | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | کارگران آماده‌سازی غذا | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | کارگران جابه‌جایی دستی بار، کالا و مصالح | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | قصابان و بسته‌بندی‌کنندگان گوشت</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
